--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/10 Octubre/Liquidacióncvs -oct/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5911" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A669079-81B0-4CCA-8DB2-B5B77416D2CB}"/>
+  <xr:revisionPtr revIDLastSave="5916" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80D6F8BF-25B3-4C6B-83C6-A6BECB72E2DA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja2" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$3650</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$3756</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33024,7 +33024,7 @@
         <v>46310</v>
       </c>
       <c r="B1243" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C1243">
         <v>1002148260</v>
@@ -33128,7 +33128,7 @@
         <v>46310</v>
       </c>
       <c r="B1247" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C1247">
         <v>1002148260</v>
@@ -68670,7 +68670,7 @@
         <v>46310</v>
       </c>
       <c r="B2614" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C2614">
         <v>1002148260</v>
@@ -87338,7 +87338,7 @@
         <v>46310</v>
       </c>
       <c r="B3332" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C3332">
         <v>1002148260</v>
@@ -97277,7 +97277,7 @@
       <c r="A3759" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H3650" xr:uid="{14AE435F-C8B7-4B0C-8617-5994DE6D3EA0}"/>
+  <autoFilter ref="A1:H3756" xr:uid="{14AE435F-C8B7-4B0C-8617-5994DE6D3EA0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/10 Octubre/Liquidacióncvs -oct/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5916" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80D6F8BF-25B3-4C6B-83C6-A6BECB72E2DA}"/>
+  <xr:revisionPtr revIDLastSave="5933" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2897FA4-DE72-4154-AC1B-3B15D6509598}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja2" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$3756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$3757</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14926" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14930" uniqueCount="101">
   <si>
     <t>Sucursal</t>
   </si>
@@ -336,6 +336,12 @@
   </si>
   <si>
     <t>Sara Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>Lider Marcela Valencia Tabares</t>
+  </si>
+  <si>
+    <t>Julieth Acevedo Gutierrez</t>
   </si>
 </sst>
 </file>
@@ -920,10 +926,10 @@
         <v>10004443161</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
         <v>51</v>
@@ -3234,10 +3240,10 @@
         <v>10004443161</v>
       </c>
       <c r="D97" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E97" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F97" t="s">
         <v>48</v>
@@ -3338,10 +3344,10 @@
         <v>10004443161</v>
       </c>
       <c r="D101" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E101" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F101" t="s">
         <v>50</v>
@@ -7602,10 +7608,10 @@
         <v>10004443161</v>
       </c>
       <c r="D265" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E265" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F265" t="s">
         <v>51</v>
@@ -8720,10 +8726,10 @@
         <v>10004443161</v>
       </c>
       <c r="D308" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E308" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F308" t="s">
         <v>51</v>
@@ -9942,10 +9948,10 @@
         <v>10004443161</v>
       </c>
       <c r="D355" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E355" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F355" t="s">
         <v>48</v>
@@ -10488,10 +10494,10 @@
         <v>10004443161</v>
       </c>
       <c r="D376" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E376" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F376" t="s">
         <v>48</v>
@@ -15324,10 +15330,10 @@
         <v>10004443161</v>
       </c>
       <c r="D562" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E562" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F562" t="s">
         <v>51</v>
@@ -22812,10 +22818,10 @@
         <v>10004443161</v>
       </c>
       <c r="D850" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E850" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F850" t="s">
         <v>50</v>
@@ -22864,10 +22870,10 @@
         <v>10004443161</v>
       </c>
       <c r="D852" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E852" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F852" t="s">
         <v>48</v>
@@ -22890,10 +22896,10 @@
         <v>10004443161</v>
       </c>
       <c r="D853" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E853" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F853" t="s">
         <v>48</v>
@@ -22994,10 +23000,10 @@
         <v>10004443161</v>
       </c>
       <c r="D857" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E857" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F857" t="s">
         <v>48</v>
@@ -24606,10 +24612,10 @@
         <v>10004443161</v>
       </c>
       <c r="D919" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E919" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F919" t="s">
         <v>50</v>
@@ -32536,10 +32542,10 @@
         <v>10004443161</v>
       </c>
       <c r="D1224" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1224" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1224" t="s">
         <v>51</v>
@@ -32692,10 +32698,10 @@
         <v>10004443161</v>
       </c>
       <c r="D1230" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1230" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1230" t="s">
         <v>48</v>
@@ -40648,10 +40654,10 @@
         <v>10004443161</v>
       </c>
       <c r="D1536" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1536" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1536" t="s">
         <v>48</v>
@@ -40674,10 +40680,10 @@
         <v>10004443161</v>
       </c>
       <c r="D1537" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1537" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1537" t="s">
         <v>50</v>
@@ -44886,10 +44892,10 @@
         <v>10004443161</v>
       </c>
       <c r="D1699" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1699" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1699" t="s">
         <v>48</v>
@@ -45640,10 +45646,10 @@
         <v>10004443161</v>
       </c>
       <c r="D1728" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1728" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1728" t="s">
         <v>51</v>
@@ -45770,10 +45776,10 @@
         <v>10004443161</v>
       </c>
       <c r="D1733" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1733" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1733" t="s">
         <v>51</v>
@@ -47434,10 +47440,10 @@
         <v>10004443161</v>
       </c>
       <c r="D1797" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1797" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1797" t="s">
         <v>51</v>
@@ -50060,10 +50066,10 @@
         <v>10004443161</v>
       </c>
       <c r="D1898" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1898" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1898" t="s">
         <v>50</v>
@@ -50788,10 +50794,10 @@
         <v>10004443161</v>
       </c>
       <c r="D1926" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1926" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1926" t="s">
         <v>51</v>
@@ -54896,10 +54902,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2084" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2084" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2084" t="s">
         <v>50</v>
@@ -56378,10 +56384,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2141" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2141" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2141" t="s">
         <v>48</v>
@@ -60330,10 +60336,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2293" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2293" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2293" t="s">
         <v>50</v>
@@ -62384,10 +62390,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2372" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2372" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2372" t="s">
         <v>51</v>
@@ -62436,10 +62442,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2374" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2374" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2374" t="s">
         <v>51</v>
@@ -63164,10 +63170,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2402" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2402" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2402" t="s">
         <v>50</v>
@@ -63346,10 +63352,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2409" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2409" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2409" t="s">
         <v>50</v>
@@ -65686,10 +65692,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2499" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2499" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2499" t="s">
         <v>48</v>
@@ -65868,10 +65874,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2506" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2506" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2506" t="s">
         <v>48</v>
@@ -71354,10 +71360,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2717" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2717" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2717" t="s">
         <v>51</v>
@@ -71380,10 +71386,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2718" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2718" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2718" t="s">
         <v>51</v>
@@ -74318,10 +74324,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2831" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2831" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2831" t="s">
         <v>51</v>
@@ -78270,10 +78276,10 @@
         <v>10004443161</v>
       </c>
       <c r="D2983" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2983" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2983" t="s">
         <v>50</v>
@@ -87110,10 +87116,10 @@
         <v>10004443161</v>
       </c>
       <c r="D3323" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E3323" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3323" t="s">
         <v>50</v>
@@ -88020,10 +88026,10 @@
         <v>10004443161</v>
       </c>
       <c r="D3358" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E3358" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3358" t="s">
         <v>50</v>
@@ -89450,10 +89456,10 @@
         <v>10004443161</v>
       </c>
       <c r="D3413" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E3413" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3413" t="s">
         <v>51</v>
@@ -89502,10 +89508,10 @@
         <v>10004443161</v>
       </c>
       <c r="D3415" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E3415" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3415" t="s">
         <v>50</v>
@@ -96991,7 +96997,7 @@
         <v>2938000</v>
       </c>
     </row>
-    <row r="3745" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3745" s="2">
         <v>46298</v>
       </c>
@@ -97014,7 +97020,7 @@
         <v>637000</v>
       </c>
     </row>
-    <row r="3746" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3746" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3746" s="2">
         <v>46296</v>
       </c>
@@ -97037,7 +97043,7 @@
         <v>575000</v>
       </c>
     </row>
-    <row r="3747" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3747" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3747" s="2">
         <v>46300</v>
       </c>
@@ -97060,7 +97066,7 @@
         <v>2198900</v>
       </c>
     </row>
-    <row r="3748" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3748" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3748" s="2">
         <v>46296</v>
       </c>
@@ -97083,7 +97089,7 @@
         <v>751000</v>
       </c>
     </row>
-    <row r="3749" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3749" s="2">
         <v>46296</v>
       </c>
@@ -97106,7 +97112,7 @@
         <v>1874500</v>
       </c>
     </row>
-    <row r="3750" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3750" s="2">
         <v>46301</v>
       </c>
@@ -97129,7 +97135,7 @@
         <v>879000</v>
       </c>
     </row>
-    <row r="3751" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3751" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3751" s="2">
         <v>46300</v>
       </c>
@@ -97152,7 +97158,7 @@
         <v>1114000</v>
       </c>
     </row>
-    <row r="3752" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3752" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3752" s="2">
         <v>46300</v>
       </c>
@@ -97163,10 +97169,10 @@
         <v>10004443161</v>
       </c>
       <c r="D3752" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E3752" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3752" s="3" t="s">
         <v>83</v>
@@ -97175,7 +97181,7 @@
         <v>845000</v>
       </c>
     </row>
-    <row r="3753" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3753" s="2">
         <v>46296</v>
       </c>
@@ -97198,7 +97204,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="3754" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3754" s="2">
         <v>46302</v>
       </c>
@@ -97221,7 +97227,7 @@
         <v>1007000</v>
       </c>
     </row>
-    <row r="3755" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3755" s="2">
         <v>46297</v>
       </c>
@@ -97244,7 +97250,7 @@
         <v>587000</v>
       </c>
     </row>
-    <row r="3756" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3756" s="2">
         <v>46298</v>
       </c>
@@ -97267,17 +97273,40 @@
         <v>265000</v>
       </c>
     </row>
-    <row r="3757" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3757" s="2"/>
-    </row>
-    <row r="3758" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3757" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3757" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B3757" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3757">
+        <v>11284350761</v>
+      </c>
+      <c r="D3757" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3757" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3757" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3757" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3757">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3758" s="2"/>
     </row>
-    <row r="3759" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3759" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H3756" xr:uid="{14AE435F-C8B7-4B0C-8617-5994DE6D3EA0}"/>
+  <autoFilter ref="A1:H3757" xr:uid="{14AE435F-C8B7-4B0C-8617-5994DE6D3EA0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
